--- a/lab-standards/BKMEA-lab-standard.xlsx
+++ b/lab-standards/BKMEA-lab-standard.xlsx
@@ -563,6 +563,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -578,6 +582,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -647,7 +655,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -669,7 +679,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -691,7 +703,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -713,7 +727,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -735,7 +751,9 @@
       <c r="C20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -757,7 +775,9 @@
       <c r="C21" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -779,7 +799,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -801,7 +823,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -823,7 +847,9 @@
       <c r="C24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -845,7 +871,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -867,7 +895,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -889,7 +919,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
@@ -911,7 +943,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>9</v>
       </c>
@@ -933,7 +967,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>9</v>
       </c>
@@ -955,7 +991,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>9</v>
       </c>
@@ -977,7 +1015,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>9</v>
       </c>
@@ -1123,6 +1163,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1138,6 +1182,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1207,7 +1255,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -1229,7 +1279,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -1251,7 +1303,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -1273,7 +1327,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -1295,7 +1351,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1317,7 +1375,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -1339,7 +1399,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -1361,7 +1423,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -1383,7 +1447,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -1405,7 +1471,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -1427,7 +1495,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -1449,7 +1519,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -1471,7 +1543,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -1493,7 +1567,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -1515,7 +1591,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -1537,7 +1615,9 @@
       <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -1559,7 +1639,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1581,7 +1663,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1727,6 +1811,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1741,6 +1829,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1810,7 +1902,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1832,7 +1926,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1854,7 +1950,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -1876,7 +1974,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -1898,7 +1998,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -1920,7 +2022,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -1942,7 +2046,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -1964,7 +2070,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -1986,7 +2094,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -2008,7 +2118,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -2030,7 +2142,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -2052,7 +2166,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -2198,6 +2314,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2213,6 +2333,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2282,7 +2406,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2304,7 +2430,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2326,7 +2454,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2348,7 +2478,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -2370,7 +2502,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -2392,7 +2526,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -2414,7 +2550,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2436,7 +2574,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -2458,7 +2598,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -2480,7 +2622,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -2502,7 +2646,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -2524,7 +2670,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -2546,7 +2694,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -2692,6 +2842,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2707,6 +2861,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2776,7 +2934,9 @@
       <c r="C16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -2798,7 +2958,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2820,7 +2982,9 @@
       <c r="C18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -2842,7 +3006,9 @@
       <c r="C19" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -2864,7 +3030,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -2886,7 +3054,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -2908,7 +3078,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2930,7 +3102,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -2952,7 +3126,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -2974,7 +3150,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -2996,7 +3174,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -3142,6 +3322,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3156,6 +3340,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3225,7 +3413,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3247,7 +3437,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3269,7 +3461,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3291,7 +3485,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -3313,7 +3509,9 @@
       <c r="C20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -3335,7 +3533,9 @@
       <c r="C21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -3357,7 +3557,9 @@
       <c r="C22" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -3379,7 +3581,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -3401,7 +3605,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -3423,7 +3629,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>9</v>
       </c>
@@ -3445,7 +3653,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>9</v>
       </c>
@@ -3467,7 +3677,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -3489,7 +3701,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>9</v>
       </c>
@@ -3511,7 +3725,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>9</v>
       </c>
@@ -3533,7 +3749,9 @@
       <c r="C30" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -3555,7 +3773,9 @@
       <c r="C31" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -3577,7 +3797,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -3599,7 +3821,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -3621,7 +3845,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>8</v>
       </c>
@@ -3767,6 +3993,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3782,6 +4012,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3851,7 +4085,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3873,7 +4109,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3895,7 +4133,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3917,7 +4157,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -3939,7 +4181,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -3961,7 +4205,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -3983,7 +4229,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -4005,7 +4253,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>10</v>
       </c>
@@ -4027,7 +4277,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -4173,6 +4425,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4188,6 +4444,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4257,7 +4517,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -4279,7 +4541,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -4301,7 +4565,9 @@
       <c r="C18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -4323,7 +4589,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -4345,7 +4613,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -4367,7 +4637,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -4389,7 +4661,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -4411,7 +4685,9 @@
       <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -4433,7 +4709,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -4455,7 +4733,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -4477,7 +4757,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -4499,7 +4781,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -4521,7 +4805,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -4543,7 +4829,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>

--- a/lab-standards/BKMEA-lab-standard.xlsx
+++ b/lab-standards/BKMEA-lab-standard.xlsx
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -3082,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -3561,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -4233,7 +4233,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -4281,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -4737,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -4761,7 +4761,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -4809,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
